--- a/other/data_structure.xlsx
+++ b/other/data_structure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theis/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theis/Documents/Dock folder/Repos/borrow-system/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF8419E4-CB6E-494C-B205-49EADE214AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60E2839-2482-BA4C-84EA-796C6C355CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21060" xr2:uid="{0FD4345E-3C03-C649-886B-D7B5C204183A}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21060" activeTab="1" xr2:uid="{0FD4345E-3C03-C649-886B-D7B5C204183A}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -77,9 +77,6 @@
     <t>Kamera</t>
   </si>
   <si>
-    <t>can_borrow-role</t>
-  </si>
-  <si>
     <t>loan_code</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>18-08-2025_10-00</t>
+  </si>
+  <si>
+    <t>can_borrow_role</t>
   </si>
 </sst>
 </file>
@@ -548,7 +548,7 @@
         <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -597,19 +597,19 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -623,16 +623,16 @@
         <v>12345678</v>
       </c>
       <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -650,10 +650,10 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">

--- a/other/data_structure.xlsx
+++ b/other/data_structure.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/theis/Documents/Dock folder/Repos/borrow-system/other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60E2839-2482-BA4C-84EA-796C6C355CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FF59ED-AC53-0B4E-AD9D-60A7570865F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21060" activeTab="1" xr2:uid="{0FD4345E-3C03-C649-886B-D7B5C204183A}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="21060" activeTab="3" xr2:uid="{0FD4345E-3C03-C649-886B-D7B5C204183A}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -644,6 +644,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1EEF17-40C2-DB4F-8E23-51BF5E4A676E}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="19" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
